--- a/marketing_surveys/027_marketing_role_assessment--marketing_surveys.xlsx
+++ b/marketing_surveys/027_marketing_role_assessment--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing_manager',_'value':_'marketing_manager'}</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing Manager', 'value': 'marketing_manager'}</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing_coordinator',_'value':_'marketing_coordinator'}</t>
+          <t>marketing_coordinator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing Coordinator', 'value': 'marketing_coordinator'}</t>
+          <t>Marketing Coordinator</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing_specialist',_'value':_'marketing_specialist'}</t>
+          <t>marketing_specialist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing Specialist', 'value': 'marketing_specialist'}</t>
+          <t>Marketing Specialist</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'social_media_marketing',_'value':_'social_media_marketing'}</t>
+          <t>social_media_marketing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Social media marketing', 'value': 'social_media_marketing'}</t>
+          <t>Social media marketing</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email_marketing',_'value':_'email_marketing'}</t>
+          <t>email_marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email marketing', 'value': 'email_marketing'}</t>
+          <t>Email marketing</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'content_creation',_'value':_'content_creation'}</t>
+          <t>content_creation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Content creation', 'value': 'content_creation'}</t>
+          <t>Content creation</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'data_analysis',_'value':_'data_analysis'}</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Data analysis', 'value': 'data_analysis'}</t>
+          <t>Data analysis</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'web_development',_'value':_'web_development'}</t>
+          <t>web_development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Web development', 'value': 'web_development'}</t>
+          <t>Web development</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'graphic_design',_'value':_'graphic_design'}</t>
+          <t>graphic_design</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Graphic design', 'value': 'graphic_design'}</t>
+          <t>Graphic design</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'beginner',_'value':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Beginner', 'value': 'beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'intermediate',_'value':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Intermediate', 'value': 'intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'advanced',_'value':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Advanced', 'value': 'advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
